--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486543_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486543_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2306</v>
+        <v>3.1017</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4917</v>
+        <v>2.5169</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7389</v>
+        <v>0.5848</v>
       </c>
       <c r="G2" t="n">
         <v>0.0201</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3203</v>
+        <v>0.1914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3341</v>
+        <v>0.3593</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0138</v>
+        <v>-0.1679</v>
       </c>
       <c r="V2" t="n">
         <v>2.4552</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.048</v>
+        <v>3.0009</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9381</v>
+        <v>4.2301</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8901</v>
+        <v>-1.2291</v>
       </c>
       <c r="G3" t="n">
         <v>2.6435</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2294</v>
+        <v>0.1824</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6165</v>
+        <v>-0.3245</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8459</v>
+        <v>0.5068</v>
       </c>
       <c r="V3" t="n">
         <v>-1.13</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6475</v>
+        <v>3.0003</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8315</v>
+        <v>2.9685</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.184</v>
+        <v>0.0318</v>
       </c>
       <c r="G4" t="n">
         <v>0.6852</v>
@@ -766,13 +766,13 @@
         <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2551</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1286</v>
+        <v>0.2656</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3837</v>
+        <v>-0.1679</v>
       </c>
       <c r="V4" t="n">
         <v>1.13</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4697</v>
+        <v>0.6142</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3867</v>
+        <v>2.7162</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9171</v>
+        <v>-2.102</v>
       </c>
       <c r="G5" t="n">
         <v>0.0083</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5038</v>
+        <v>0.6483</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7487</v>
+        <v>0.0781</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7551</v>
+        <v>0.5702</v>
       </c>
       <c r="V5" t="n">
         <v>-1.13</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. KRISTENSEN</t>
+          <t>C. ROGERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7307</v>
+        <v>0.4246</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6026</v>
+        <v>1.5437</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8719</v>
+        <v>-1.1191</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4719</v>
+        <v>-0.0406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6239</v>
+        <v>-0.1896</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6605</v>
+        <v>1.6951</v>
       </c>
       <c r="K6" t="n">
-        <v>0.584</v>
+        <v>1.0799</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>0.6152</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1324</v>
+        <v>-1.7357</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.432</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7004</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3326</v>
+        <v>-0.2971</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9421</v>
+        <v>-0.1514</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3904</v>
+        <v>-0.1457</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. LO</t>
+          <t>T. ROBERTS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6032</v>
+        <v>0.0927</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0515</v>
+        <v>2.5287</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4483</v>
+        <v>-2.436</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6374</v>
+        <v>-2.2481</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1162</v>
+        <v>-3.9989</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5212</v>
+        <v>1.7507</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6449</v>
+        <v>1.2311</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6173</v>
+        <v>-2.77</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2622</v>
+        <v>4.0011</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2823</v>
+        <v>-3.4792</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4989</v>
+        <v>-1.2289</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7834</v>
+        <v>-2.2504</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5021</v>
+        <v>0.4056</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7557</v>
+        <v>-0.0276</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2536</v>
+        <v>0.4332</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3491</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3491</v>
+        <v>1.3252</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ROGERS</t>
+          <t>D. KRISTENSEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4686</v>
+        <v>0.0545</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8046</v>
+        <v>0.9573</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2732</v>
+        <v>-0.9028</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0406</v>
+        <v>-0.4719</v>
       </c>
       <c r="H8" t="n">
-        <v>0.149</v>
+        <v>0.152</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1896</v>
+        <v>-0.6239</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6951</v>
+        <v>0.6605</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0799</v>
+        <v>0.584</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6152</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7357</v>
+        <v>-1.1324</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.432</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.7004</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1903</v>
+        <v>0.6564</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8904</v>
+        <v>0.2968</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2998</v>
+        <v>0.3596</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. ROBERTS</t>
+          <t>O. LO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2033</v>
+        <v>-0.2656</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5409</v>
+        <v>1.1827</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7442</v>
+        <v>-1.4483</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2481</v>
+        <v>-1.6374</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.9989</v>
+        <v>-1.1162</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7507</v>
+        <v>-0.5212</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2311</v>
+        <v>0.6449</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.77</v>
+        <v>-0.6173</v>
       </c>
       <c r="L9" t="n">
-        <v>4.0011</v>
+        <v>1.2622</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4792</v>
+        <v>-2.2823</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2289</v>
+        <v>-0.4989</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2504</v>
+        <v>-1.7834</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8904</v>
+        <v>0.6333</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0154</v>
+        <v>0.8869</v>
       </c>
       <c r="U9" t="n">
-        <v>0.125</v>
+        <v>-0.2536</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1952</v>
+        <v>-0.3491</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3252</v>
+        <v>-0.3491</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2817</v>
+        <v>-1.4059</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9314</v>
+        <v>-2.0864</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6805</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4068</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5601</v>
+        <v>0.4359</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1286</v>
+        <v>-0.0264</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4315</v>
+        <v>0.4623</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0191</v>
+        <v>-1.5151</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9112</v>
+        <v>-0.2839</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1079</v>
+        <v>-1.2312</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7352</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2192</v>
+        <v>0.2848</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0154</v>
+        <v>-0.3881</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7962</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8091</v>
+        <v>-2.542</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8384</v>
+        <v>-1.6329</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9707</v>
+        <v>-0.909</v>
       </c>
       <c r="G12" t="n">
         <v>-4.5014</v>
@@ -1390,13 +1390,13 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1697</v>
+        <v>0.4368</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1334</v>
+        <v>0.0721</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3031</v>
+        <v>0.3647</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0885</v>
+        <v>-5.331</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2843</v>
+        <v>-3.5885</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8042</v>
+        <v>-1.7425</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9138</v>
@@ -1468,13 +1468,13 @@
         <v>1.5225</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5874</v>
+        <v>0.17</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0856</v>
+        <v>0.1472</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9347</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.1406</v>
+        <v>-0.7707000000000006</v>
       </c>
       <c r="E14" t="n">
-        <v>9.682299999999996</v>
+        <v>11.0524</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.823</v>
+        <v>-11.8229</v>
       </c>
       <c r="G14" t="n">
         <v>-14.5981</v>
@@ -1546,13 +1546,13 @@
         <v>15.2252</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4756</v>
+        <v>3.8454</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3062000000000002</v>
+        <v>1.0636</v>
       </c>
       <c r="U14" t="n">
-        <v>2.7819</v>
+        <v>2.7818</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8933999999999996</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5037</v>
+        <v>2.8455</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1953</v>
+        <v>2.4188</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3085</v>
+        <v>0.4267</v>
       </c>
       <c r="G15" t="n">
         <v>0.9362</v>
@@ -1624,13 +1624,13 @@
         <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8017</v>
+        <v>-0.46</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0203</v>
+        <v>0.1385</v>
       </c>
       <c r="V15" t="n">
         <v>2.8042</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>D. LOVE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0726</v>
+        <v>1.8947</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3923</v>
+        <v>2.9997</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3196</v>
+        <v>-1.105</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1667</v>
+        <v>3.7808</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2709</v>
+        <v>0.8515</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8958</v>
+        <v>2.9293</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7128</v>
+        <v>4.836</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5237000000000001</v>
+        <v>1.3354</v>
       </c>
       <c r="L16" t="n">
-        <v>4.1891</v>
+        <v>3.5006</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5461</v>
+        <v>-1.0552</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2528</v>
+        <v>-0.4838</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2933</v>
+        <v>-0.5714</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4845</v>
+        <v>-0.3413</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1454</v>
+        <v>-0.0517</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6299</v>
+        <v>-0.2896</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.056</v>
+        <v>0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.056</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. LOVE</t>
+          <t>M. LAPORNIK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0064</v>
+        <v>1.8372</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1115</v>
+        <v>2.8066</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.105</v>
+        <v>-0.9694</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7808</v>
+        <v>3.6218</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8515</v>
+        <v>1.3532</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9293</v>
+        <v>2.2687</v>
       </c>
       <c r="J17" t="n">
-        <v>4.836</v>
+        <v>4.5863</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3354</v>
+        <v>1.4084</v>
       </c>
       <c r="L17" t="n">
-        <v>3.5006</v>
+        <v>3.1779</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0552</v>
+        <v>-0.9645</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4838</v>
+        <v>-0.0552</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5714</v>
+        <v>-0.9093</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.7401</v>
+        <v>-0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R17" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2295</v>
+        <v>-0.8586</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0601</v>
+        <v>-0.6922</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2896</v>
+        <v>-0.1665</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1952</v>
+        <v>-0.491</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3904</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-0.491</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1552</v>
+        <v>1.6398</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4142</v>
+        <v>2.057</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.259</v>
+        <v>-0.4172</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5367</v>
+        <v>4.1667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6873</v>
+        <v>0.2709</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8495</v>
+        <v>3.8958</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8061</v>
+        <v>4.7128</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6387</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1674</v>
+        <v>4.1891</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2694</v>
+        <v>-0.5461</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0486</v>
+        <v>-0.2528</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.318</v>
+        <v>-0.2933</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5087</v>
+        <v>0.0517</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6081</v>
+        <v>-0.4807</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0994</v>
+        <v>0.5323</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>-1.056</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1076</v>
+        <v>0.8452</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5554</v>
+        <v>2.2814</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5522</v>
+        <v>-1.4362</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7171999999999999</v>
+        <v>1.4932</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6264</v>
+        <v>1.8916</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.3984</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7884</v>
+        <v>2.1969</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8067</v>
+        <v>2.0439</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0183</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0712</v>
+        <v>-0.7038</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1803</v>
+        <v>-0.1523</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1091</v>
+        <v>-0.5514</v>
       </c>
       <c r="P19" t="n">
         <v>-0.87</v>
@@ -1936,28 +1936,28 @@
         <v>0.2175</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6422</v>
+        <v>0.1481</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1454</v>
+        <v>0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7876</v>
+        <v>0.106</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6183</v>
+        <v>0.074</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6183</v>
+        <v>-1.056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0995</v>
+        <v>0.8007</v>
       </c>
       <c r="E20" t="n">
-        <v>2.5049</v>
+        <v>1.9672</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4054</v>
+        <v>-1.1665</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4932</v>
+        <v>1.5367</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8916</v>
+        <v>0.6873</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3984</v>
+        <v>0.8495</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1969</v>
+        <v>1.8061</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0439</v>
+        <v>0.6387</v>
       </c>
       <c r="L20" t="n">
-        <v>0.153</v>
+        <v>1.1674</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7038</v>
+        <v>-0.2694</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1523</v>
+        <v>0.0486</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5514</v>
+        <v>-0.318</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4024</v>
+        <v>0.1541</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2656</v>
+        <v>0.161</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1369</v>
+        <v>-0.0069</v>
       </c>
       <c r="V20" t="n">
-        <v>0.074</v>
+        <v>-1.3252</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.056</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. LAPORNIK</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0446</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>2.4713</v>
+        <v>0.2202</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4267</v>
+        <v>0.5162</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6218</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3532</v>
+        <v>0.6264</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2687</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5863</v>
+        <v>1.7884</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4084</v>
+        <v>1.8067</v>
       </c>
       <c r="L21" t="n">
-        <v>3.1779</v>
+        <v>-0.0183</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9645</v>
+        <v>-1.0712</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0552</v>
+        <v>-1.1803</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9093</v>
+        <v>0.1091</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6511</v>
+        <v>0.271</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0274</v>
+        <v>-0.4807</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6237</v>
+        <v>0.7516</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.491</v>
+        <v>0.6183</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.491</v>
+        <v>0.6183</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.9426</v>
       </c>
       <c r="E22" t="n">
         <v>-0.7508</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.161</v>
+        <v>-0.1918</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6497000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2621</v>
+        <v>-0.2929</v>
       </c>
       <c r="T22" t="n">
         <v>-0.137</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1251</v>
+        <v>-0.1559</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1701</v>
+        <v>-2.7424</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1874</v>
+        <v>-1.8521</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9828</v>
+        <v>-0.8903</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7261</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6029</v>
+        <v>-0.1751</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4795</v>
+        <v>-0.1442</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1234</v>
+        <v>-0.031</v>
       </c>
       <c r="V23" t="n">
         <v>1.2039</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7672</v>
+        <v>-4.0286</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8837</v>
+        <v>-0.3249</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8835</v>
+        <v>-3.7037</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2786</v>
@@ -2326,13 +2326,13 @@
         <v>0.87</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.966</v>
+        <v>-0.2274</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9589</v>
+        <v>-0.4002</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0071</v>
+        <v>0.1727</v>
       </c>
       <c r="V24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.1405</v>
+        <v>2.8859</v>
       </c>
       <c r="E25" t="n">
-        <v>11.823</v>
+        <v>11.8231</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.6823</v>
+        <v>-8.937199999999999</v>
       </c>
       <c r="G25" t="n">
         <v>14.5982</v>
@@ -2386,10 +2386,10 @@
         <v>12.9412</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.061999999999999</v>
+        <v>-8.062000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.005599999999999</v>
+        <v>-5.0056</v>
       </c>
       <c r="O25" t="n">
         <v>-3.0563</v>
@@ -2404,13 +2404,13 @@
         <v>4.35</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4755</v>
+        <v>-1.7304</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.7818</v>
+        <v>-2.782</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3064</v>
+        <v>1.0512</v>
       </c>
       <c r="V25" t="n">
         <v>0.8933999999999997</v>
